--- a/outputs/evaluation/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/CF_M01_req_eval.xlsx
@@ -492,7 +492,7 @@
         <v>0.8387</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6706</v>
+        <v>0.7238</v>
       </c>
     </row>
     <row r="5">
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8667</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8667</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
         <v>26</v>
@@ -760,13 +760,13 @@
         <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
         <v>26</v>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3845</v>
+        <v>0.3751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>That the system saves the actions carried out on the platform</t>
+          <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -1038,16 +1038,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_R09</t>
+          <t>CF_M01_R03</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3852</v>
+        <v>0.4443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The system shall allow authorized users to list the playlogs.</t>
+          <t>The system shall store the connections of the players.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -1074,11 +1074,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Be able to list the different playlogs of the system</t>
+          <t>System saves player connections</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4262</v>
+        <v>0.4656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>The actions that the user will be able to see will depend on the permissions what does it have</t>
+          <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1148,16 +1148,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_29</t>
+          <t>R_13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_R27</t>
+          <t>CF_M01_R13</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4378</v>
+        <v>0.4828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1166,19 +1166,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Users shall only be able to observe confidential data belonging to their own user account.</t>
+          <t>The connections visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1188,18 +1188,18 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Users can only view their confidential data user and no one else.</t>
+          <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CF_M01_R026</t>
+          <t>CF_M01_R12</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -1207,67 +1207,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_R12</t>
+          <t>CF_M01_R27</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4381</v>
+        <v>0.4865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The system shall allow authorized users to list the connections of the players.</t>
+          <t>Users shall only be able to observe the confidential data of their own user account.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>R_28</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Be able to list the different player connections in the system</t>
+          <t>Users can only view their confidential data user and no one else.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CF_M01_R026</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M01_R25</t>
+          <t>CF_M01_R10</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4609</v>
+        <v>0.4891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,19 +1284,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Users without permission shall not be able to access data for which they do not have authorization.</t>
+          <t>The playlogs visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>R_26</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1298,18 +1306,18 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Unauthorized users cannot access data they do not own.</t>
+          <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CF_M01_R024</t>
+          <t>CF_M01_R09</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1317,16 +1325,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_03</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_R03</t>
+          <t>CF_M01_R15</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4742</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,12 +1343,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The system shall store the connections of the players.</t>
+          <t>The system shall allow users with permissions to list the different actions performed on the platform entities.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1353,11 +1361,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Let the system save player connections</t>
+          <t>Be able to list the different actions that are carried out on the different
+platform entities</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1368,134 +1377,134 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_13</t>
+          <t>R_01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M01_R13</t>
+          <t>CF_M01_R01</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4808</v>
+        <v>0.543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The connections visible to the user shall depend on their assigned permissions.</t>
+          <t>The system shall store the playlogs of the players.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The connections that the user will be able to see will depend on the permissions you have.</t>
+          <t>System saves the players' playlogs</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>CF_M01_R12</t>
-        </is>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R_10</t>
+          <t>R_20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_R10</t>
+          <t>CF_M01_R20</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.4999</v>
+        <v>0.5964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The playlogs visible to the user shall depend on their assigned permissions.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>R_09</t>
-        </is>
-      </c>
+          <t>The system must be available at all times, except for scheduled updates.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Availability and reliability</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>CF_M01_R09</t>
-        </is>
-      </c>
+          <t>The system must be available at all times, except for some punctuality, such as an update.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>12d. Availability and reliability</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_R01</t>
+          <t>CF_M01_R12</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.5523</v>
+        <v>0.6706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1504,12 +1513,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The system shall store the playlogs of the players.</t>
+          <t>The system shall allow users with permissions to list the different connections of the players in the system.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1522,11 +1531,11 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>That the system saves the players' playlogs</t>
+          <t>Be able to list the different player connections in the system</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1537,83 +1546,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R_20</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_R20</t>
+          <t>CF_M01_R09</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.5756</v>
+        <v>0.6864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The system shall be available at all times, except for scheduled updates.</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Availability and reliability</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ISO/IEC 25010</t>
-        </is>
-      </c>
+          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>The system must be available at all times, except for some punctuality, such as an update.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>12d. Availability and reliability</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>Be able to list the different playlogs of the system</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R_22</t>
+          <t>R_28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_R22</t>
+          <t>CF_M01_R26</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.7096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1622,22 +1615,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The system shall be capable of supporting an unlimited number of concurrent connections.</t>
+          <t>Confidential user information must be protected to ensure privacy.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Privacy</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ISO/IEC 25010</t>
+          <t>Volere</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1648,17 +1641,17 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>The system must be able to support an unlimited number of
-connections at the same time.</t>
+          <t>Users' confidential information must be protected in order to
+guarantee your privacy.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12f. Capacity</t>
+          <t>15c. Privacy</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1672,16 +1665,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_R07</t>
+          <t>CF_M01_R08</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.6679</v>
+        <v>0.7406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1695,7 +1688,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Each action must have a date, client, user, and player assigned.</t>
+          <t>All actions must be performed on a platform entity.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1716,7 +1709,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Each action has an assigned date, client and player.</t>
+          <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1731,84 +1724,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M01_R26</t>
+          <t>CF_M01_R07</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7124</v>
+        <v>0.7759</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Confidential user information must be protected to ensure privacy.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ISO/IEC 25010</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Each action must have a date, client, user, and assigned player.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>R_06</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Users' confidential information must be protected in order to
-guarantee your privacy.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>15c. Privacy</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>Each action has an assigned date, client and player.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CF_M01_R06</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_04</t>
+          <t>R_17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_R04</t>
+          <t>CF_M01_R17</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.763</v>
+        <v>0.8153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1817,19 +1801,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Each connection must have a date, client, and player assigned.</t>
+          <t>All actions must be related to a platform entity.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>R_03</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1839,18 +1823,18 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Each connection has an assigned date, client, player.</t>
+          <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CF_M01_R03</t>
+          <t>CF_M01_R015</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1858,16 +1842,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_R02</t>
+          <t>CF_M01_R04</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7766</v>
+        <v>0.8748</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1881,14 +1865,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Each playlog must have a date, client, and player assigned.</t>
+          <t>Each connection must have a date, client, and assigned player.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1902,14 +1886,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Each playlog has an assigned date, client, player.</t>
+          <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CF_M01_R01</t>
+          <t>CF_M01_R03</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -1917,16 +1901,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M01_R11</t>
+          <t>CF_M01_R02</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7966</v>
+        <v>0.8821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1935,19 +1919,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The user must be able to view all details of the playlog.</t>
+          <t>Each playlog must have a date, client, and assigned player.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_01</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1957,18 +1941,18 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>You must be able to see all the details of the playlog.</t>
+          <t>Each playlog has an assigned date, client, player.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CF_M01_R09</t>
+          <t>CF_M01_R01</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -1976,84 +1960,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R_26</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_R24</t>
+          <t>CF_M01_R19</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.8642</v>
+        <v>0.907</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>System functionalities shall only be accessible to users with the corresponding permissions.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Access</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>ISO/IEC 25010</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>The system shall respond to any user action in less than 5 seconds.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>R_18</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>The project's functionalities must only be accessible to
-users with the corresponding permissions.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>15a. Access</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>The system responds to any user action in less than 5 seconds.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CF_M01_R018</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_19</t>
+          <t>R_11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_R19</t>
+          <t>CF_M01_R11</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9135</v>
+        <v>0.9115</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2062,19 +2037,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The system shall respond to any user action in less than 5 seconds.</t>
+          <t>The user must be able to see all details of the playlog.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>R_18</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -2084,18 +2059,18 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The system responds to any user action in less than 5 seconds.</t>
+          <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CF_M01_R018</t>
+          <t>CF_M01_R09</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
@@ -2103,265 +2078,267 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_18</t>
+          <t>R_21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_R18</t>
+          <t>CF_M01_R21</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.931</v>
+        <v>0.9352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The system shall respond quickly when the user performs an action.</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Speed and latency</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ISO/IEC 25010</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Any user must be able to access the platform at any time of the day, except during scheduled updates.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>R_20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The system must respond quickly when the user performs any action.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>12a. Speed and latency</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>Any user must be able to access the platform during any time
+time of day. Except for scheduled updates.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CF_M01_R020</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_R21</t>
+          <t>CF_M01_R24</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9343</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Any user must be able to access the platform at any time of the day, except during scheduled updates.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>R_20</t>
-        </is>
-      </c>
+          <t>The project functionalities must only be accessible to users with the corresponding permissions.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Any user must be able to access the platform during any time
-time of day. Except for scheduled updates.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>CF_M01_R020</t>
-        </is>
-      </c>
+          <t>The project's functionalities must only be accessible to
+users with the corresponding permissions.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R_24</t>
+          <t>R_14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_R23</t>
+          <t>CF_M01_R14</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9462</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The system shall be able to grow in capacity when the volume of data increases.</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Scalability</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ISO/IEC 25010</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Connections can only have two states: connected or not connected.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>R_12</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>The system must be able to grow in capacity as the volume of data increases.</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>12g. Scalability</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>Connections can only have two states: connected or not connected.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>CF_M01_R12</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R_14</t>
+          <t>R_22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_R14</t>
+          <t>CF_M01_R22</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9674</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Connections shall only have two states: connected or not connected.</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
+          <t>The system must be able to support an unlimited number of connections at the same time.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Connections can only have two states: connected or not connected.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>CF_M01_R12</t>
-        </is>
-      </c>
+          <t>The system must be able to support an unlimited number of
+connections at the same time.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>12f. Capacity</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R_17</t>
+          <t>R_24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CF_M01_R17</t>
+          <t>CF_M01_R23</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2369,58 +2346,66 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>All actions must be related to an entity of the platform.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
+          <t>The system must be able to grow in capacity when the volume of data increases.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>All actions must be related to an entity the platform.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>CF_M01_R015</t>
-        </is>
-      </c>
+          <t>The system must be able to grow in capacity as the volume of data increases.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>12g. Scalability</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>R_08</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CF_M01_R08</t>
+          <t>CF_M01_R18</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2428,47 +2413,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All actions must be performed on an entity of the platform.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>R_06</t>
-        </is>
-      </c>
+          <t>The system must respond quickly when the user performs any action.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Speed and latency</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>All actions are performed on an entity of the platform.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>CF_M01_R06</t>
-        </is>
-      </c>
+          <t>The system must respond quickly when the user performs any action.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2579,37 +2572,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_15</t>
+          <t>R_23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The system shall allow authorized users to list the actions performed on the platform entities.</t>
+          <t>The platform shall scale dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M01_R08</t>
+          <t>CF_M01_R05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>All actions are performed on an entity of the platform.</t>
+          <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.5184</v>
+        <v>0.1564</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>R_25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2619,27 +2612,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The platform shall scale dynamically with changes in simultaneous connections.</t>
+          <t>The system shall scale automatically as data increases.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M01_R05</t>
+          <t>CF_M01_R23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The connection status can only be connected or not connected.</t>
+          <t>The system must be able to grow in capacity as the volume of data increases.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.156</v>
+        <v>0.3857</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_25</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2649,21 +2642,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The system shall scale automatically as data increases.</t>
+          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CF_M01_R23</t>
+          <t>CF_M01_R25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The system must be able to grow in capacity as the volume of data increases.</t>
+          <t>Unauthorized users cannot access data they do not own.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3909</v>
+        <v>0.3483</v>
       </c>
     </row>
   </sheetData>
@@ -2715,32 +2708,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_R15</t>
+          <t>CF_M01_R25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Be able to list the different actions that are carried out on the different
-platform entities</t>
+          <t>Unauthorized users cannot access data they do not own.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_15</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The system shall allow authorized users to list the actions performed on the platform entities.</t>
+          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.326</v>
+        <v>0.3483</v>
       </c>
     </row>
     <row r="3">
@@ -2761,16 +2753,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Each action must have a date, client, user, and player assigned.</t>
+          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.1132</v>
+        <v>0.2428</v>
       </c>
     </row>
     <row r="4">
@@ -2800,7 +2792,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3212</v>
+        <v>0.3222</v>
       </c>
     </row>
     <row r="5">
@@ -2826,11 +2818,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The system shall allow authorized users to list the connections of the players.</t>
+          <t>The system shall allow users with permissions to list the different connections of the players in the system.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1579</v>
+        <v>0.2979</v>
       </c>
     </row>
     <row r="6">
@@ -2860,7 +2852,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.2956</v>
+        <v>0.2963</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/CF_M01_req_eval.xlsx
@@ -450,13 +450,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8966</v>
+        <v>0.9565</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8387</v>
+        <v>0.7333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7282</v>
+        <v>0.6692</v>
       </c>
     </row>
     <row r="5">
@@ -591,22 +591,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -641,22 +641,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -681,7 +681,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -706,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -856,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,67 +949,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_06</t>
+          <t>R_27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CF_M01_R06</t>
+          <t>CF_M01_R24</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3752</v>
+        <v>0.3583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The system shall store the actions performed on the platform.</t>
+          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>R_26</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>System saves the actions carried out on the platform</t>
+          <t>Unauthorized users cannot access data they do not own.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>CF_M01_R023</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R_03</t>
+          <t>R_06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CF_M01_R03</t>
+          <t>CF_M01_R06</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.453</v>
+        <v>0.3986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,12 +1026,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The system shall store the connections of the players.</t>
+          <t>The system shall store the actions performed on the platform.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -1036,11 +1044,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>System saves player connections</t>
+          <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -1051,75 +1059,67 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R_16</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CF_M01_R16</t>
+          <t>CF_M01_R03</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.4619</v>
+        <v>0.4466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The actions visible to the user shall depend on their assigned permissions.</t>
+          <t>The system shall store the connections of the players.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>R_15</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>The actions that the user will be able to see will depend on the permissions it has</t>
+          <t>System saves player connections</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>CF_M01_R015</t>
-        </is>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R_13</t>
+          <t>R_16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M01_R13</t>
+          <t>CF_M01_R16</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4794</v>
+        <v>0.4649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,19 +1128,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>The connections visible to the user shall depend on their assigned permissions.</t>
+          <t>The actions visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1150,18 +1150,18 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>The connections that the user will be able to see will depend on the permissions it has.</t>
+          <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CF_M01_R12</t>
+          <t>CF_M01_R015</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -1169,16 +1169,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R_10</t>
+          <t>R_13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M01_R10</t>
+          <t>CF_M01_R13</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4857</v>
+        <v>0.4818</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,14 +1192,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The playlogs visible to the user shall depend on their assigned permissions.</t>
+          <t>The connections visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1213,14 +1213,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
+          <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CF_M01_R09</t>
+          <t>CF_M01_R12</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.4864</v>
+        <v>0.4848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CF_M01_R026</t>
+          <t>CF_M01_R025</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1287,53 +1287,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R_15</t>
+          <t>R_10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M01_R15</t>
+          <t>CF_M01_R10</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5419</v>
+        <v>0.4877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different actions performed on the platform entities.</t>
+          <t>The playlogs visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R_09</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Be able to list the different actions that are carried out on the different
-platform entities</t>
+          <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CF_M01_R09</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1390,146 +1397,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R_20</t>
+          <t>R_15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M01_R20</t>
+          <t>CF_M01_R15</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5965</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The system must be available at all times, except for scheduled updates.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Availability and reliability</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system shall allow users with permissions to list the different actions performed on the platform entities.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The system must be available at all times, except for some punctuality, such as an update.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>12d. Availability and reliability</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>Be able to list the different actions that are carried out on the different
+platform entities</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R_07</t>
+          <t>R_20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M01_R07</t>
+          <t>CF_M01_R20</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6723</v>
+        <v>0.5914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Each action must have a date, client, user, and player assigned.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>R_06</t>
-        </is>
-      </c>
+          <t>The system must be available at all times, except for scheduled updates.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Availability and reliability</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Each action has an assigned date, client and player.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>CF_M01_R06</t>
-        </is>
-      </c>
+          <t>The system must be available at all times, except for some punctuality, such as an update.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>12d. Availability and reliability</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M01_R09</t>
+          <t>CF_M01_R07</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6846</v>
+        <v>0.6693</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1539,16 +1539,20 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
+          <t>Each action must have a date, client, user, and player assigned.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>R_06</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1556,27 +1560,31 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Be able to list the different playlogs of the system</t>
+          <t>Each action has an assigned date, client and player.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CF_M01_R06</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M01_R12</t>
+          <t>CF_M01_R09</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.6906</v>
+        <v>0.6801</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1590,7 +1598,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
+          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1607,7 +1615,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Be able to list the different player connections in the system</t>
+          <t>Be able to list the different playlogs of the system</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1618,143 +1626,135 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R_28</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M01_R26</t>
+          <t>CF_M01_R12</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.7099</v>
+        <v>0.6834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Confidential user information must be protected to ensure privacy.</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Privacy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>36</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Be able to list the different player connections in the system</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R_28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CF_M01_R25</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7111</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Confidential user information must be protected to ensure privacy.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
         <v>39</v>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Users' confidential information must be protected in order to
 guarantee your privacy.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>15c. Privacy</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Volere</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R_04</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CF_M01_R04</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Each connection must have a date, client, and player assigned.</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>R_03</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>35</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Each connection has an assigned date, client, player.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>CF_M01_R03</t>
-        </is>
-      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M01_R02</t>
+          <t>CF_M01_R04</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7805</v>
+        <v>0.7641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1768,14 +1768,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Each playlog must have a date, client, and player assigned.</t>
+          <t>Each connection must have a date, client, and player assigned.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>R_01</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1789,14 +1789,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Each playlog has an assigned date, client, player.</t>
+          <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CF_M01_R01</t>
+          <t>CF_M01_R03</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1804,143 +1804,143 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R_22</t>
+          <t>R_02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M01_R22</t>
+          <t>CF_M01_R02</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.859</v>
+        <v>0.7792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>QR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The system must be capable of supporting an unlimited number of connections at the same time.</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Each playlog must have a date, client, and player assigned.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>R_01</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>35</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Each playlog has an assigned date, client, player.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CF_M01_R01</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R_22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CF_M01_R21</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8585</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>QR</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The system must be capable of supporting an unlimited number of connections at the same time.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
         <v>38</v>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>The system must be able to support an unlimited number of
 connections at the same time.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>12f. Capacity</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Volere</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>R_19</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CF_M01_R19</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>The system shall respond to any user action in less than 5 seconds.</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>R_18</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>37</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>The system responds to any user action in less than 5 seconds.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>CF_M01_R018</t>
-        </is>
-      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R_11</t>
+          <t>R_19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M01_R11</t>
+          <t>CF_M01_R19</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9115</v>
+        <v>0.9064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1949,19 +1949,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The user must be able to see all details of the playlog.</t>
+          <t>The system shall respond to any user action in less than 5 seconds.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1971,18 +1971,18 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>You must be able to see all the details of the playlog.</t>
+          <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CF_M01_R09</t>
+          <t>CF_M01_R018</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -1990,72 +1990,79 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R_21</t>
+          <t>R_26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M01_R21</t>
+          <t>CF_M01_R23</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9353</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Any user must be able to access the platform at any time of the day, except during scheduled updates.</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>R_20</t>
-        </is>
-      </c>
+          <t>The project functionalities must only be accessible to users with the corresponding permissions.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Criterion</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Any user must be able to access the platform during any time
-time of day. Except for scheduled updates.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>CF_M01_R020</t>
-        </is>
-      </c>
+          <t>The project's functionalities must only be accessible to users with the corresponding permissions.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Volere</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R_26</t>
+          <t>R_18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CF_M01_R24</t>
+          <t>CF_M01_R18</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2068,17 +2075,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>The project functionalities must only be accessible to users with the corresponding permissions.</t>
+          <t>The system must respond quickly when the user performs any action.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Speed and latency</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2094,17 +2101,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>The project's functionalities must only be accessible to
-users with the corresponding permissions.</t>
+          <t>The system must respond quickly when the user performs any action.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>15a. Access</t>
+          <t>12a. Speed and latency</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2118,12 +2124,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R_18</t>
+          <t>R_24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CF_M01_R18</t>
+          <t>CF_M01_R22</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2136,17 +2142,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>The system must respond quickly when the user performs any action.</t>
+          <t>The system must be able to grow in capacity when the volume of data increases.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Speed and latency</t>
+          <t>Scalability</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2162,16 +2168,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The system must respond quickly when the user performs any action.</t>
+          <t>The system must be able to grow in capacity as the volume of data increases.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>12a. Speed and latency</t>
+          <t>12g. Scalability</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2185,12 +2191,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R_17</t>
+          <t>R_14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CF_M01_R17</t>
+          <t>CF_M01_R14</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2203,19 +2209,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>All actions must be related to an entity of the platform.</t>
+          <t>Connections can only have two states: connected or not connected.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>R_15</t>
+          <t>R_12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -2225,18 +2231,18 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>All actions must be related to an entity the platform.</t>
+          <t>Connections can only have two states: connected or not connected.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CF_M01_R015</t>
+          <t>CF_M01_R12</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2244,12 +2250,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R_08</t>
+          <t>R_05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF_M01_R08</t>
+          <t>CF_M01_R05</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2262,19 +2268,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>All actions must be performed on an entity of the platform.</t>
+          <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>R_06</t>
+          <t>R_03</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2284,206 +2290,21 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>All actions are performed on an entity of the platform.</t>
+          <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CF_M01_R06</t>
+          <t>CF_M01_R03</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>R_24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CF_M01_R23</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>The system must be able to grow in capacity when the volume of data increases.</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Scalability</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>QR</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>38</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>The system must be able to grow in capacity as the volume of data increases.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>12g. Scalability</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>R_05</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CF_M01_R05</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>The connection status can only be connected or not connected.</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>R_03</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>35</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>The connection status can only be connected or not connected.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>CF_M01_R03</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>R_14</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>CF_M01_R14</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Connections can only have two states: connected or not connected.</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>36</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Connections can only have two states: connected or not connected.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>CF_M01_R12</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2496,132 +2317,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>LLM_ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>LLM_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LLM_description</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>closest_GT_ID</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>closest_GT_description</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>similarity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>R_23</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The platform shall scale dynamically with changes in simultaneous connections.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CF_M01_R05</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>The connection status can only be connected or not connected.</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.1564</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R_25</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>The system shall scale automatically as data increases.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CF_M01_R23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>The system must be able to grow in capacity as the volume of data increases.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3877</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R_27</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CF_M01_R25</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Unauthorized users cannot access data they do not own.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3481</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2632,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2670,7 +2368,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M01_R25</t>
+          <t>CF_M01_R08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2680,67 +2378,67 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unauthorized users cannot access data they do not own.</t>
+          <t>All actions are performed on an entity of the platform.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>R_27</t>
+          <t>R_06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Users without permission shall not be able to access data for which they do not have permission.</t>
+          <t>The system shall store the actions performed on the platform.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.3481</v>
+        <v>0.6781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M01_R28</t>
+          <t>CF_M01_R11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A customer may have different users</t>
+          <t>You must be able to see all the details of the playlog.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R_09</t>
+          <t>R_01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
+          <t>The system shall store the playlogs of the players.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.2434</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M01_R29</t>
+          <t>CF_M01_R17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Constraint</t>
+          <t>Criterion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The users are the ones who execute the actions in the platform</t>
+          <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2754,13 +2452,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3186</v>
+        <v>0.3905</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M01_R30</t>
+          <t>CF_M01_R28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2770,51 +2468,111 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The users may have different players that reproduce contents</t>
+          <t>A customer may have different users</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>R_12</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
+          <t>The system shall allow users with permissions to list the different playlogs of the system.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.2574</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CF_M01_R29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The users are the ones who execute the actions in the platform</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R_06</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The system shall store the actions performed on the platform.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3462</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M01_R30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Constraint</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The users may have different players that reproduce contents</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R_12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>The system shall allow users with permissions to list the different player connections of the system.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2545</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>CF_M01_R31</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Constraint</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Players are connected a given amount of time</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>0.2969</v>
+      <c r="F8" t="n">
+        <v>0.2924</v>
       </c>
     </row>
   </sheetData>
